--- a/data/CReDEs/v4/dg_blzd.xlsx
+++ b/data/CReDEs/v4/dg_blzd.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EB78862-1AF5-4339-AAF1-8A5BE3DE8BA7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69C2552-6E0E-43D2-8D7B-0D46B0BC6BAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{77CF7729-489F-4928-9833-E8D0A48313B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="179021" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="135">
   <si>
     <t>标签类型</t>
   </si>
@@ -478,10 +478,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写符合描述的内容，若没有描述则填写"未描述",请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>请填写以下选项：无，大结节型，小结节型，混合型，未描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -511,6 +507,14 @@
   </si>
   <si>
     <t>请填写符合描述的内容，单位为"个",若没有描述则填写"未描述",请填写以下选项：无，有，未描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写符合描述的内容，若没有描述则填写"未描述",请填写以下选项：Ⅰ级，Ⅱ级，Ⅲ级，Ⅳ级，未描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写符合描述的内容，若没有描述则填写"未描述",请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：无，正常，异常，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1328,7 +1332,7 @@
         <v>104</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>85</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1580,7 +1584,7 @@
         <v>124</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1601,7 +1605,7 @@
         <v>91</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1616,13 +1620,13 @@
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>91</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1637,13 +1641,13 @@
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>130</v>
-      </c>
       <c r="G31" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -1658,13 +1662,13 @@
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>104</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/data/CReDEs/v4/dg_blzd.xlsx
+++ b/data/CReDEs/v4/dg_blzd.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C69C2552-6E0E-43D2-8D7B-0D46B0BC6BAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F841540-56A7-459C-9D4B-60E3942EE065}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{77CF7729-489F-4928-9833-E8D0A48313B1}"/>
   </bookViews>
@@ -514,7 +514,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写符合描述的内容，若没有描述则填写"未描述",请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：无，正常，异常，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述</t>
+    <t>请填写符合描述的内容，若没有描述则填写"未描述",请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/data/CReDEs/v4/dg_blzd.xlsx
+++ b/data/CReDEs/v4/dg_blzd.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\桌面\东肝\CReDEs\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F841540-56A7-459C-9D4B-60E3942EE065}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8DB4BE-23A5-4B52-9177-3B6FFF882698}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135" xr2:uid="{77CF7729-489F-4928-9833-E8D0A48313B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021" concurrentCalc="0"/>
+  <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -414,10 +414,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>请填写以下选项：MVI：0；（MVI：1）；（MVI：2）；未描述</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>术后病理_血管侵犯</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -515,6 +511,10 @@
   </si>
   <si>
     <t>请填写符合描述的内容，若没有描述则填写"未描述",请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述,请填写以下选项：阴性，阳性，未描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>请填写以下选项：MVI：0；MVI：1；MVI：2；未描述</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1332,7 +1332,7 @@
         <v>104</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -1431,13 +1431,13 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>91</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -1452,13 +1452,13 @@
       </c>
       <c r="D22" s="10"/>
       <c r="E22" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>104</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -1494,13 +1494,13 @@
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="5" t="s">
         <v>114</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -1515,13 +1515,13 @@
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>16</v>
@@ -1557,13 +1557,13 @@
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -1578,13 +1578,13 @@
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="F28" s="14" t="s">
-        <v>124</v>
-      </c>
       <c r="G28" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
@@ -1605,7 +1605,7 @@
         <v>91</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -1620,13 +1620,13 @@
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>91</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -1641,13 +1641,13 @@
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>129</v>
-      </c>
       <c r="G31" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -1662,13 +1662,13 @@
       </c>
       <c r="D32" s="9"/>
       <c r="E32" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>104</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
